--- a/results/breakdown/2020/nitrous oxide production, AON 90 cryogenic, green ammonia.xlsx
+++ b/results/breakdown/2020/nitrous oxide production, AON 90 cryogenic, green ammonia.xlsx
@@ -429,7 +429,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>1.922929400243709</v>
+        <v>1.922929400243707</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -446,7 +446,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.7379373656224572</v>
+        <v>0.7379373656224562</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -463,7 +463,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0006378931697709082</v>
+        <v>0.000637893169770908</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -480,7 +480,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.04032311907425682</v>
+        <v>0.04032311907425683</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -497,7 +497,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.001726448290475418</v>
+        <v>0.001726448290475419</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -514,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>1.114975585307987</v>
+        <v>1.114975585307986</v>
       </c>
       <c r="E7">
         <v>1</v>
